--- a/devices.xlsx
+++ b/devices.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14290" windowHeight="10940"/>
+    <workbookView windowWidth="15550" windowHeight="8150"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>device_type</t>
   </si>
@@ -43,6 +43,21 @@
     <t>password</t>
   </si>
   <si>
+    <t>vlan_id</t>
+  </si>
+  <si>
+    <t>vlan_name</t>
+  </si>
+  <si>
+    <t>interface</t>
+  </si>
+  <si>
+    <t>ip_address</t>
+  </si>
+  <si>
+    <t>subnet_mask</t>
+  </si>
+  <si>
     <t>huawei</t>
   </si>
   <si>
@@ -55,10 +70,34 @@
     <t>admin123</t>
   </si>
   <si>
+    <t>VLAN10</t>
+  </si>
+  <si>
+    <t>GE0/0/1</t>
+  </si>
+  <si>
+    <t>192.168.10.1</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">192.168.100.11 </t>
   </si>
   <si>
+    <t>VLAN20</t>
+  </si>
+  <si>
+    <t>192.168.20.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">192.168.100.12 </t>
+  </si>
+  <si>
+    <t>VLAN30</t>
+  </si>
+  <si>
+    <t>192.168.30.1</t>
   </si>
 </sst>
 </file>
@@ -71,13 +110,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -224,7 +269,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,6 +278,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -418,11 +469,22 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -544,55 +606,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
@@ -607,75 +666,87 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -989,16 +1060,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.8181818181818" customWidth="1"/>
+    <col min="1" max="1" width="13.0909090909091" customWidth="1"/>
     <col min="2" max="2" width="16.2727272727273" customWidth="1"/>
-    <col min="3" max="3" width="16.3636363636364" customWidth="1"/>
-    <col min="4" max="4" width="15.8181818181818" customWidth="1"/>
+    <col min="3" max="3" width="13.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="6" width="11.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="10.3636363636364" customWidth="1"/>
+    <col min="8" max="8" width="12.5454545454545" customWidth="1"/>
+    <col min="9" max="9" width="12.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" ht="17" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1011,48 +1086,111 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="17" spans="1:9">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="E2" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="17" spans="1:9">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="E3" s="1">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" ht="17" spans="1:9">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:9">
+      <c r="H5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
